--- a/Output/Validation_metrics.xlsx
+++ b/Output/Validation_metrics.xlsx
@@ -450,19 +450,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0354363262543203</v>
+        <v>0.0351981199819385</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0038410843561904</v>
+        <v>0.00346366316030073</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0604350859786063</v>
+        <v>0.0599615343885311</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0120420930353177</v>
+        <v>0.0119636801899664</v>
       </c>
       <c r="F2" t="n">
-        <v>0.745538746697221</v>
+        <v>0.750149842792548</v>
       </c>
     </row>
     <row r="3">
@@ -470,19 +470,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>0.031653426861624</v>
+        <v>0.0318748373542021</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00533243041924015</v>
+        <v>0.00514677911229114</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0531244305650029</v>
+        <v>0.0533072946322924</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0143504220414621</v>
+        <v>0.0141444577055995</v>
       </c>
       <c r="F3" t="n">
-        <v>0.354954692786679</v>
+        <v>0.355442352005878</v>
       </c>
     </row>
     <row r="4">
@@ -490,19 +490,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0346591123905659</v>
+        <v>0.0342309544234731</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00263921964376976</v>
+        <v>0.00275823252680921</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0612446118391278</v>
+        <v>0.0607523069468153</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00900393472148489</v>
+        <v>0.00914026443472812</v>
       </c>
       <c r="F4" t="n">
-        <v>0.750989017925249</v>
+        <v>0.755350365716413</v>
       </c>
     </row>
     <row r="5">
@@ -510,19 +510,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0176316660299161</v>
+        <v>0.017682849615286</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00460350321760583</v>
+        <v>0.00451959009943494</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0261316513950109</v>
+        <v>0.0260905999535254</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00711561442881194</v>
+        <v>0.00685547956246628</v>
       </c>
       <c r="F5" t="n">
-        <v>0.566986796169366</v>
+        <v>0.569024119993513</v>
       </c>
     </row>
     <row r="6">
@@ -530,19 +530,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0184830181240756</v>
+        <v>0.0186237920095098</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00349402585286641</v>
+        <v>0.00356647381319139</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0278445875069637</v>
+        <v>0.0280019064903268</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00835721404371188</v>
+        <v>0.00843587149833791</v>
       </c>
       <c r="F6" t="n">
-        <v>0.484443676938336</v>
+        <v>0.480517753614363</v>
       </c>
     </row>
     <row r="7">
@@ -550,19 +550,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0162424813085747</v>
+        <v>0.0162124571663334</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000860489183039798</v>
+        <v>0.000950375601324568</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0246976128881119</v>
+        <v>0.0247172730045338</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00361150670748</v>
+        <v>0.00362163788190944</v>
       </c>
       <c r="F7" t="n">
-        <v>0.573836870303085</v>
+        <v>0.572914652315874</v>
       </c>
     </row>
     <row r="8">
@@ -570,19 +570,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0177869280418395</v>
+        <v>0.017852250478781</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00416824685749879</v>
+        <v>0.00430340995174879</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0262487707140768</v>
+        <v>0.0263624126052424</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00638599647471897</v>
+        <v>0.00643182560029843</v>
       </c>
       <c r="F8" t="n">
-        <v>0.562244513605429</v>
+        <v>0.560328079422306</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +654,7 @@
         <v>226</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
@@ -663,25 +663,25 @@
         <v>27</v>
       </c>
       <c r="H2" t="n">
-        <v>1840.36824682238</v>
+        <v>1840.36823517677</v>
       </c>
       <c r="I2" t="n">
-        <v>1801.99182724524</v>
+        <v>1801.99181200741</v>
       </c>
       <c r="J2" t="n">
-        <v>-10.8012495097916</v>
+        <v>-10.8012481544542</v>
       </c>
       <c r="K2" t="n">
-        <v>10.8012495097916</v>
+        <v>10.8012481544542</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0335490101245386</v>
+        <v>0.0339123816757315</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0502762690871849</v>
+        <v>0.0502354375337958</v>
       </c>
       <c r="N2" t="n">
-        <v>0.880051397777374</v>
+        <v>0.880264010783644</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +698,7 @@
         <v>226</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F3" t="n">
         <v>5</v>
@@ -707,25 +707,25 @@
         <v>27</v>
       </c>
       <c r="H3" t="n">
-        <v>1839.19026927675</v>
+        <v>1839.1902197493</v>
       </c>
       <c r="I3" t="n">
-        <v>1805.36530090489</v>
+        <v>1805.3652231757</v>
       </c>
       <c r="J3" t="n">
-        <v>-10.6041668004709</v>
+        <v>-10.6041632358704</v>
       </c>
       <c r="K3" t="n">
-        <v>10.6041668004709</v>
+        <v>10.6041632358704</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0311686226509289</v>
+        <v>0.0315482233862146</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0471220159832712</v>
+        <v>0.0467695558101382</v>
       </c>
       <c r="N3" t="n">
-        <v>0.798726181768245</v>
+        <v>0.798477100409068</v>
       </c>
     </row>
     <row r="4">
@@ -742,7 +742,7 @@
         <v>228</v>
       </c>
       <c r="E4" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
@@ -751,25 +751,25 @@
         <v>27</v>
       </c>
       <c r="H4" t="n">
-        <v>1872.56426628889</v>
+        <v>1872.56429169333</v>
       </c>
       <c r="I4" t="n">
-        <v>1838.89265231379</v>
+        <v>1838.89271043588</v>
       </c>
       <c r="J4" t="n">
-        <v>-10.0655439486328</v>
+        <v>-10.0655522142696</v>
       </c>
       <c r="K4" t="n">
-        <v>10.0655439486328</v>
+        <v>10.0655522142696</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0413263458077946</v>
+        <v>0.0405831515139641</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0755507464222674</v>
+        <v>0.0750346422305731</v>
       </c>
       <c r="N4" t="n">
-        <v>0.567883997187231</v>
+        <v>0.575911271100093</v>
       </c>
     </row>
     <row r="5">
@@ -786,7 +786,7 @@
         <v>228</v>
       </c>
       <c r="E5" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
@@ -795,25 +795,25 @@
         <v>27</v>
       </c>
       <c r="H5" t="n">
-        <v>1838.99300199594</v>
+        <v>1838.9930031951</v>
       </c>
       <c r="I5" t="n">
-        <v>1806.04427489122</v>
+        <v>1806.04429802595</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.363921123269</v>
+        <v>-10.3639194007398</v>
       </c>
       <c r="K5" t="n">
-        <v>10.363921123269</v>
+        <v>10.3639194007398</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0344478854408614</v>
+        <v>0.0335745938479491</v>
       </c>
       <c r="M5" t="n">
-        <v>0.060358074377152</v>
+        <v>0.0590922034109284</v>
       </c>
       <c r="N5" t="n">
-        <v>0.822949837103842</v>
+        <v>0.831984706874697</v>
       </c>
     </row>
     <row r="6">
@@ -830,7 +830,7 @@
         <v>229</v>
       </c>
       <c r="E6" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -839,25 +839,25 @@
         <v>27</v>
       </c>
       <c r="H6" t="n">
-        <v>1874.48578813563</v>
+        <v>1874.48560482544</v>
       </c>
       <c r="I6" t="n">
-        <v>1842.3774273698</v>
+        <v>1842.37709953643</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.7953709192036</v>
+        <v>-10.7953808633949</v>
       </c>
       <c r="K6" t="n">
-        <v>10.7953709192036</v>
+        <v>10.7953808633949</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0366897672474778</v>
+        <v>0.0363722494858331</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0688683240231562</v>
+        <v>0.0686758329572203</v>
       </c>
       <c r="N6" t="n">
-        <v>0.712584000871103</v>
+        <v>0.713025885492623</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         <v>188</v>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
@@ -883,25 +883,25 @@
         <v>27</v>
       </c>
       <c r="H7" t="n">
-        <v>1459.61578740894</v>
+        <v>1459.61635331063</v>
       </c>
       <c r="I7" t="n">
-        <v>1434.54302235029</v>
+        <v>1434.54373519085</v>
       </c>
       <c r="J7" t="n">
-        <v>-11.0685655405802</v>
+        <v>-11.068799358432</v>
       </c>
       <c r="K7" t="n">
-        <v>11.0685655405802</v>
+        <v>11.068799358432</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0309771781915633</v>
+        <v>0.0309189809999111</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0487800579763462</v>
+        <v>0.0487202358092714</v>
       </c>
       <c r="N7" t="n">
-        <v>0.486962673466682</v>
+        <v>0.489605925375022</v>
       </c>
     </row>
     <row r="8">
@@ -918,7 +918,7 @@
         <v>190</v>
       </c>
       <c r="E8" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
@@ -927,25 +927,25 @@
         <v>27</v>
       </c>
       <c r="H8" t="n">
-        <v>1492.14340745345</v>
+        <v>1492.14346058988</v>
       </c>
       <c r="I8" t="n">
-        <v>1461.60065570108</v>
+        <v>1461.60073000162</v>
       </c>
       <c r="J8" t="n">
-        <v>-11.1201814671283</v>
+        <v>-11.1201929076427</v>
       </c>
       <c r="K8" t="n">
-        <v>11.1201814671283</v>
+        <v>11.1201929076427</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0295880076259951</v>
+        <v>0.0304476507801569</v>
       </c>
       <c r="M8" t="n">
-        <v>0.043998773279126</v>
+        <v>0.0443673106918452</v>
       </c>
       <c r="N8" t="n">
-        <v>0.499264667798599</v>
+        <v>0.497961480390042</v>
       </c>
     </row>
     <row r="9">
@@ -962,7 +962,7 @@
         <v>190</v>
       </c>
       <c r="E9" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F9" t="n">
         <v>5</v>
@@ -971,25 +971,25 @@
         <v>27</v>
       </c>
       <c r="H9" t="n">
-        <v>1472.02130449627</v>
+        <v>1472.02057092473</v>
       </c>
       <c r="I9" t="n">
-        <v>1442.99246715511</v>
+        <v>1442.99173711115</v>
       </c>
       <c r="J9" t="n">
-        <v>-10.2990617702771</v>
+        <v>-10.2988351754255</v>
       </c>
       <c r="K9" t="n">
-        <v>10.2990617702771</v>
+        <v>10.2988351754255</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0366669806941431</v>
+        <v>0.0369315907360562</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0642825271915885</v>
+        <v>0.064478107383891</v>
       </c>
       <c r="N9" t="n">
-        <v>0.259259118709709</v>
+        <v>0.251812392214572</v>
       </c>
     </row>
     <row r="10">
@@ -1006,7 +1006,7 @@
         <v>190</v>
       </c>
       <c r="E10" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -1015,25 +1015,25 @@
         <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>1496.81816312452</v>
+        <v>1496.81810399523</v>
       </c>
       <c r="I10" t="n">
-        <v>1470.69590422185</v>
+        <v>1470.69579155594</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.1904235302674</v>
+        <v>-11.190447138007</v>
       </c>
       <c r="K10" t="n">
-        <v>11.1904235302674</v>
+        <v>11.190447138007</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0241417669597915</v>
+        <v>0.0244609063719431</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0370407391444524</v>
+        <v>0.0375777878927693</v>
       </c>
       <c r="N10" t="n">
-        <v>0.539156689248318</v>
+        <v>0.529065666496163</v>
       </c>
     </row>
     <row r="11">
@@ -1050,7 +1050,7 @@
         <v>191</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
@@ -1059,25 +1059,25 @@
         <v>27</v>
       </c>
       <c r="H11" t="n">
-        <v>1495.35764603296</v>
+        <v>1495.35756821174</v>
       </c>
       <c r="I11" t="n">
-        <v>1466.6139294176</v>
+        <v>1466.61391080554</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.391195640068</v>
+        <v>-10.3911666329237</v>
       </c>
       <c r="K11" t="n">
-        <v>10.391195640068</v>
+        <v>10.3911666329237</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0368932008366272</v>
+        <v>0.0366150578829432</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0715200552335013</v>
+        <v>0.0713930313836852</v>
       </c>
       <c r="N11" t="n">
-        <v>0.173572838813811</v>
+        <v>0.182537549280462</v>
       </c>
     </row>
     <row r="12">
@@ -1094,7 +1094,7 @@
         <v>216</v>
       </c>
       <c r="E12" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F12" t="n">
         <v>5</v>
@@ -1103,25 +1103,25 @@
         <v>27</v>
       </c>
       <c r="H12" t="n">
-        <v>1758.73935681322</v>
+        <v>1758.7392324782</v>
       </c>
       <c r="I12" t="n">
-        <v>1716.68097527068</v>
+        <v>1716.68079610106</v>
       </c>
       <c r="J12" t="n">
-        <v>-10.566607141103</v>
+        <v>-10.5665917663867</v>
       </c>
       <c r="K12" t="n">
-        <v>10.566607141103</v>
+        <v>10.5665917663867</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0333558703935564</v>
+        <v>0.0330473694752033</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0569282993574167</v>
+        <v>0.0563445322341992</v>
       </c>
       <c r="N12" t="n">
-        <v>0.862823912510961</v>
+        <v>0.866737684571742</v>
       </c>
     </row>
     <row r="13">
@@ -1138,7 +1138,7 @@
         <v>216</v>
       </c>
       <c r="E13" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F13" t="n">
         <v>5</v>
@@ -1147,25 +1147,25 @@
         <v>27</v>
       </c>
       <c r="H13" t="n">
-        <v>1753.57084636933</v>
+        <v>1753.57085002214</v>
       </c>
       <c r="I13" t="n">
-        <v>1715.71108102072</v>
+        <v>1715.71108756488</v>
       </c>
       <c r="J13" t="n">
-        <v>-10.4052945928871</v>
+        <v>-10.4052931253909</v>
       </c>
       <c r="K13" t="n">
-        <v>10.4052945928871</v>
+        <v>10.4052931253909</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0328814665816486</v>
+        <v>0.0319865443141016</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0490787817518992</v>
+        <v>0.0484733903930213</v>
       </c>
       <c r="N13" t="n">
-        <v>0.868582514316533</v>
+        <v>0.870439384555166</v>
       </c>
     </row>
     <row r="14">
@@ -1182,7 +1182,7 @@
         <v>218</v>
       </c>
       <c r="E14" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
@@ -1191,25 +1191,25 @@
         <v>27</v>
       </c>
       <c r="H14" t="n">
-        <v>1776.74491054865</v>
+        <v>1776.74484159385</v>
       </c>
       <c r="I14" t="n">
-        <v>1742.37135749885</v>
+        <v>1742.37120869822</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.5583984327499</v>
+        <v>-10.5584040261443</v>
       </c>
       <c r="K14" t="n">
-        <v>10.5583984327499</v>
+        <v>10.5584040261443</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0389647745052</v>
+        <v>0.0386544477123124</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0695677131505042</v>
+        <v>0.0693128306697678</v>
       </c>
       <c r="N14" t="n">
-        <v>0.630652835701162</v>
+        <v>0.63310278866399</v>
       </c>
     </row>
     <row r="15">
@@ -1226,7 +1226,7 @@
         <v>219</v>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F15" t="n">
         <v>5</v>
@@ -1235,25 +1235,25 @@
         <v>27</v>
       </c>
       <c r="H15" t="n">
-        <v>1770.86622859955</v>
+        <v>1770.86618890965</v>
       </c>
       <c r="I15" t="n">
-        <v>1732.94774745062</v>
+        <v>1732.94770121922</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.65229930072839</v>
+        <v>-9.65229681010347</v>
       </c>
       <c r="K15" t="n">
-        <v>9.65229930072839</v>
+        <v>9.65229681010347</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0354095705481388</v>
+        <v>0.0351350496962437</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0705722937727479</v>
+        <v>0.0701855676342241</v>
       </c>
       <c r="N15" t="n">
-        <v>0.612124195187214</v>
+        <v>0.613554578258177</v>
       </c>
     </row>
     <row r="16">
@@ -1270,7 +1270,7 @@
         <v>220</v>
       </c>
       <c r="E16" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
@@ -1279,25 +1279,25 @@
         <v>27</v>
       </c>
       <c r="H16" t="n">
-        <v>1815.51927693906</v>
+        <v>1815.519309185</v>
       </c>
       <c r="I16" t="n">
-        <v>1777.59266204959</v>
+        <v>1777.59270115762</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.5002236032532</v>
+        <v>-10.5002282930828</v>
       </c>
       <c r="K16" t="n">
-        <v>10.5002236032532</v>
+        <v>10.5002282930828</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0326838799242857</v>
+        <v>0.0323313609195042</v>
       </c>
       <c r="M16" t="n">
-        <v>0.060075971163071</v>
+        <v>0.0594452138028643</v>
       </c>
       <c r="N16" t="n">
-        <v>0.829787781499099</v>
+        <v>0.833386234462215</v>
       </c>
     </row>
     <row r="17">
@@ -1314,7 +1314,7 @@
         <v>166</v>
       </c>
       <c r="E17" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F17" t="n">
         <v>5</v>
@@ -1323,25 +1323,25 @@
         <v>27</v>
       </c>
       <c r="H17" t="n">
-        <v>1293.90970278034</v>
+        <v>1293.90967977488</v>
       </c>
       <c r="I17" t="n">
-        <v>1266.58264142255</v>
+        <v>1266.58261158762</v>
       </c>
       <c r="J17" t="n">
-        <v>-8.96935719043834</v>
+        <v>-8.96935329326783</v>
       </c>
       <c r="K17" t="n">
-        <v>8.96935719043834</v>
+        <v>8.96935329326783</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0191012654033731</v>
+        <v>0.0192706882980357</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0299348121680794</v>
+        <v>0.029850974778997</v>
       </c>
       <c r="N17" t="n">
-        <v>0.449755510657618</v>
+        <v>0.453214017503272</v>
       </c>
     </row>
     <row r="18">
@@ -1358,7 +1358,7 @@
         <v>168</v>
       </c>
       <c r="E18" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F18" t="n">
         <v>5</v>
@@ -1367,25 +1367,25 @@
         <v>27</v>
       </c>
       <c r="H18" t="n">
-        <v>1277.11140055989</v>
+        <v>1277.11144813937</v>
       </c>
       <c r="I18" t="n">
-        <v>1250.00854440025</v>
+        <v>1250.00860749403</v>
       </c>
       <c r="J18" t="n">
-        <v>-8.95634126204687</v>
+        <v>-8.95633233781006</v>
       </c>
       <c r="K18" t="n">
-        <v>8.95634126204687</v>
+        <v>8.95633233781006</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0219168828276328</v>
+        <v>0.0218939070614992</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0336286406269565</v>
+        <v>0.0334237717855494</v>
       </c>
       <c r="N18" t="n">
-        <v>0.298161716019356</v>
+        <v>0.308551909000109</v>
       </c>
     </row>
     <row r="19">
@@ -1402,7 +1402,7 @@
         <v>169</v>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F19" t="n">
         <v>5</v>
@@ -1411,25 +1411,25 @@
         <v>27</v>
       </c>
       <c r="H19" t="n">
-        <v>1286.21253318482</v>
+        <v>1286.21263349216</v>
       </c>
       <c r="I19" t="n">
-        <v>1261.53312347598</v>
+        <v>1261.5332852508</v>
       </c>
       <c r="J19" t="n">
-        <v>-9.40401985682823</v>
+        <v>-9.40402105009651</v>
       </c>
       <c r="K19" t="n">
-        <v>9.40401985682823</v>
+        <v>9.40402105009651</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0121740974912489</v>
+        <v>0.0124626437993316</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0171276671333752</v>
+        <v>0.0175119330067044</v>
       </c>
       <c r="N19" t="n">
-        <v>0.844255408846561</v>
+        <v>0.834586190142606</v>
       </c>
     </row>
     <row r="20">
@@ -1446,7 +1446,7 @@
         <v>170</v>
       </c>
       <c r="E20" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F20" t="n">
         <v>5</v>
@@ -1455,25 +1455,25 @@
         <v>27</v>
       </c>
       <c r="H20" t="n">
-        <v>1335.16278320812</v>
+        <v>1335.16276563982</v>
       </c>
       <c r="I20" t="n">
-        <v>1312.28959764136</v>
+        <v>1312.28961701329</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.87717169715784</v>
+        <v>-9.87721544746586</v>
       </c>
       <c r="K20" t="n">
-        <v>9.87717169715784</v>
+        <v>9.87721544746586</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0133347335375658</v>
+        <v>0.013268304332134</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0200768856191575</v>
+        <v>0.0201791975061876</v>
       </c>
       <c r="N20" t="n">
-        <v>0.777326781923426</v>
+        <v>0.773877567607103</v>
       </c>
     </row>
     <row r="21">
@@ -1490,7 +1490,7 @@
         <v>171</v>
       </c>
       <c r="E21" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F21" t="n">
         <v>5</v>
@@ -1499,25 +1499,25 @@
         <v>27</v>
       </c>
       <c r="H21" t="n">
-        <v>1304.45645493424</v>
+        <v>1304.45642294229</v>
       </c>
       <c r="I21" t="n">
-        <v>1279.71083135068</v>
+        <v>1279.71077597227</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.03033712397401</v>
+        <v>-9.03034150019876</v>
       </c>
       <c r="K21" t="n">
-        <v>9.03033712397401</v>
+        <v>9.03034150019876</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02163135088976</v>
+        <v>0.0215187045854294</v>
       </c>
       <c r="M21" t="n">
-        <v>0.029890251427486</v>
+        <v>0.0294871226901887</v>
       </c>
       <c r="N21" t="n">
-        <v>0.509874309634796</v>
+        <v>0.515464130019128</v>
       </c>
     </row>
     <row r="22">
@@ -1534,7 +1534,7 @@
         <v>178</v>
       </c>
       <c r="E22" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F22" t="n">
         <v>5</v>
@@ -1543,25 +1543,25 @@
         <v>27</v>
       </c>
       <c r="H22" t="n">
-        <v>1390.11684713734</v>
+        <v>1390.1167611323</v>
       </c>
       <c r="I22" t="n">
-        <v>1364.02533704741</v>
+        <v>1364.02528299957</v>
       </c>
       <c r="J22" t="n">
-        <v>-9.65119988387544</v>
+        <v>-9.65112870893039</v>
       </c>
       <c r="K22" t="n">
-        <v>9.65119988387544</v>
+        <v>9.65112870893039</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0194196123588901</v>
+        <v>0.0195619680473439</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0290520377763501</v>
+        <v>0.029199412977121</v>
       </c>
       <c r="N22" t="n">
-        <v>0.559679026304405</v>
+        <v>0.553268280744903</v>
       </c>
     </row>
     <row r="23">
@@ -1578,7 +1578,7 @@
         <v>179</v>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F23" t="n">
         <v>5</v>
@@ -1587,25 +1587,25 @@
         <v>27</v>
       </c>
       <c r="H23" t="n">
-        <v>1427.40215081453</v>
+        <v>1427.40244386756</v>
       </c>
       <c r="I23" t="n">
-        <v>1401.72644188357</v>
+        <v>1401.7269370713</v>
       </c>
       <c r="J23" t="n">
-        <v>-9.14511852756693</v>
+        <v>-9.14509687464951</v>
       </c>
       <c r="K23" t="n">
-        <v>9.14511852756693</v>
+        <v>9.14509687464951</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0222839830819762</v>
+        <v>0.0222005650717341</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0377030168875034</v>
+        <v>0.0376871279214714</v>
       </c>
       <c r="N23" t="n">
-        <v>0.35270196570945</v>
+        <v>0.354166051380318</v>
       </c>
     </row>
     <row r="24">
@@ -1622,7 +1622,7 @@
         <v>180</v>
       </c>
       <c r="E24" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F24" t="n">
         <v>5</v>
@@ -1631,25 +1631,25 @@
         <v>27</v>
       </c>
       <c r="H24" t="n">
-        <v>1448.56288131921</v>
+        <v>1448.56287354251</v>
       </c>
       <c r="I24" t="n">
-        <v>1418.54722941115</v>
+        <v>1418.5472030088</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.71459243033945</v>
+        <v>-9.7145979179985</v>
       </c>
       <c r="K24" t="n">
-        <v>9.71459243033945</v>
+        <v>9.7145979179985</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0168462798366451</v>
+        <v>0.0168136750463924</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0238662299037506</v>
+        <v>0.0238898962267759</v>
       </c>
       <c r="N24" t="n">
-        <v>0.615482846695155</v>
+        <v>0.620724170949232</v>
       </c>
     </row>
     <row r="25">
@@ -1666,7 +1666,7 @@
         <v>182</v>
       </c>
       <c r="E25" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F25" t="n">
         <v>5</v>
@@ -1675,25 +1675,25 @@
         <v>27</v>
       </c>
       <c r="H25" t="n">
-        <v>1487.21505579817</v>
+        <v>1487.21499269546</v>
       </c>
       <c r="I25" t="n">
-        <v>1457.73333195372</v>
+        <v>1457.73323095097</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.66567528292786</v>
+        <v>-9.66568339231346</v>
       </c>
       <c r="K25" t="n">
-        <v>9.66567528292786</v>
+        <v>9.66568339231346</v>
       </c>
       <c r="L25" t="n">
-        <v>0.013325540586858</v>
+        <v>0.013380946648569</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0159407509251817</v>
+        <v>0.0159681883214891</v>
       </c>
       <c r="N25" t="n">
-        <v>0.805645732630136</v>
+        <v>0.805080097868525</v>
       </c>
     </row>
     <row r="26">
@@ -1710,7 +1710,7 @@
         <v>182</v>
       </c>
       <c r="E26" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F26" t="n">
         <v>5</v>
@@ -1719,25 +1719,25 @@
         <v>27</v>
       </c>
       <c r="H26" t="n">
-        <v>1461.80325838284</v>
+        <v>1461.80324652802</v>
       </c>
       <c r="I26" t="n">
-        <v>1434.47788505819</v>
+        <v>1434.4778940094</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.87449893446263</v>
+        <v>-9.87451950304532</v>
       </c>
       <c r="K26" t="n">
-        <v>9.87449893446263</v>
+        <v>9.87451950304532</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0205396747560086</v>
+        <v>0.0211618052335094</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0326609020420326</v>
+        <v>0.0332649070047768</v>
       </c>
       <c r="N26" t="n">
-        <v>0.440661398701662</v>
+        <v>0.431435294157821</v>
       </c>
     </row>
     <row r="27">
@@ -1754,7 +1754,7 @@
         <v>222</v>
       </c>
       <c r="E27" t="n">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
@@ -1763,25 +1763,25 @@
         <v>27</v>
       </c>
       <c r="H27" t="n">
-        <v>1833.05535308583</v>
+        <v>1833.05538764071</v>
       </c>
       <c r="I27" t="n">
-        <v>1795.71846440819</v>
+        <v>1795.71849804753</v>
       </c>
       <c r="J27" t="n">
-        <v>-9.46673090838157</v>
+        <v>-9.46675952199433</v>
       </c>
       <c r="K27" t="n">
-        <v>9.46673090838157</v>
+        <v>9.46675952199433</v>
       </c>
       <c r="L27" t="n">
-        <v>0.016143429560294</v>
+        <v>0.0159169477535658</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0223017478435527</v>
+        <v>0.022192098588012</v>
       </c>
       <c r="N27" t="n">
-        <v>0.587741069843219</v>
+        <v>0.59220529356002</v>
       </c>
     </row>
     <row r="28">
@@ -1798,7 +1798,7 @@
         <v>223</v>
       </c>
       <c r="E28" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="F28" t="n">
         <v>5</v>
@@ -1807,25 +1807,25 @@
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>1856.6962260196</v>
+        <v>1856.69622782335</v>
       </c>
       <c r="I28" t="n">
-        <v>1813.92644716788</v>
+        <v>1813.92643209066</v>
       </c>
       <c r="J28" t="n">
-        <v>-8.72645824577596</v>
+        <v>-8.72646199995075</v>
       </c>
       <c r="K28" t="n">
-        <v>8.72645824577596</v>
+        <v>8.72646199995075</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0169295225035247</v>
+        <v>0.0169483643292728</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0307248654199497</v>
+        <v>0.0307565763335297</v>
       </c>
       <c r="N28" t="n">
-        <v>0.420193261912018</v>
+        <v>0.418792516975456</v>
       </c>
     </row>
     <row r="29">
@@ -1842,7 +1842,7 @@
         <v>224</v>
       </c>
       <c r="E29" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F29" t="n">
         <v>5</v>
@@ -1851,25 +1851,25 @@
         <v>27</v>
       </c>
       <c r="H29" t="n">
-        <v>1848.96083542704</v>
+        <v>1848.96084781458</v>
       </c>
       <c r="I29" t="n">
-        <v>1809.62476134216</v>
+        <v>1809.62476444441</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.00386310780307</v>
+        <v>-9.00386767331272</v>
       </c>
       <c r="K29" t="n">
-        <v>9.00386310780307</v>
+        <v>9.00386767331272</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0159172326339076</v>
+        <v>0.0157440554643462</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0221679541467598</v>
+        <v>0.0221880574527923</v>
       </c>
       <c r="N29" t="n">
-        <v>0.656707692222845</v>
+        <v>0.657373061643987</v>
       </c>
     </row>
     <row r="30">
@@ -1886,7 +1886,7 @@
         <v>225</v>
       </c>
       <c r="E30" t="n">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
@@ -1895,25 +1895,25 @@
         <v>27</v>
       </c>
       <c r="H30" t="n">
-        <v>1837.03743520593</v>
+        <v>1837.03745211185</v>
       </c>
       <c r="I30" t="n">
-        <v>1798.214101642</v>
+        <v>1798.21410055771</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.79029588610928</v>
+        <v>-8.79030640738352</v>
       </c>
       <c r="K30" t="n">
-        <v>8.79029588610928</v>
+        <v>8.79030640738352</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0171926900059304</v>
+        <v>0.0174020818929118</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0229021795263203</v>
+        <v>0.0230557579881544</v>
       </c>
       <c r="N30" t="n">
-        <v>0.565028882941233</v>
+        <v>0.560071138604411</v>
       </c>
     </row>
     <row r="31">
@@ -1930,7 +1930,7 @@
         <v>227</v>
       </c>
       <c r="E31" t="n">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="F31" t="n">
         <v>5</v>
@@ -1939,25 +1939,25 @@
         <v>27</v>
       </c>
       <c r="H31" t="n">
-        <v>1866.22296713725</v>
+        <v>1866.22668605676</v>
       </c>
       <c r="I31" t="n">
-        <v>1826.09629909674</v>
+        <v>1826.0994037022</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.40896666719166</v>
+        <v>-9.40945981205753</v>
       </c>
       <c r="K31" t="n">
-        <v>9.40896666719166</v>
+        <v>9.40945981205753</v>
       </c>
       <c r="L31" t="n">
-        <v>0.015029531839217</v>
+        <v>0.0150508363915704</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0253913175039772</v>
+        <v>0.0253938746601806</v>
       </c>
       <c r="N31" t="n">
-        <v>0.68093075972748</v>
+        <v>0.681623614280293</v>
       </c>
     </row>
     <row r="32">
@@ -1974,7 +1974,7 @@
         <v>179</v>
       </c>
       <c r="E32" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="F32" t="n">
         <v>5</v>
@@ -1983,25 +1983,25 @@
         <v>27</v>
       </c>
       <c r="H32" t="n">
-        <v>1395.36787990675</v>
+        <v>1395.36787924941</v>
       </c>
       <c r="I32" t="n">
-        <v>1365.32834210137</v>
+        <v>1365.32832327898</v>
       </c>
       <c r="J32" t="n">
-        <v>-9.19427656799706</v>
+        <v>-9.19428105991498</v>
       </c>
       <c r="K32" t="n">
-        <v>9.19427656799706</v>
+        <v>9.19428105991498</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0188864419359778</v>
+        <v>0.0192597928197857</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0291923580869116</v>
+        <v>0.0295358858232677</v>
       </c>
       <c r="N32" t="n">
-        <v>0.481912965305844</v>
+        <v>0.466495781771159</v>
       </c>
     </row>
     <row r="33">
@@ -2018,7 +2018,7 @@
         <v>181</v>
       </c>
       <c r="E33" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F33" t="n">
         <v>5</v>
@@ -2027,25 +2027,25 @@
         <v>27</v>
       </c>
       <c r="H33" t="n">
-        <v>1379.04302209568</v>
+        <v>1379.04296618075</v>
       </c>
       <c r="I33" t="n">
-        <v>1350.13159651678</v>
+        <v>1350.13160412307</v>
       </c>
       <c r="J33" t="n">
-        <v>-9.0366859944058</v>
+        <v>-9.03665996827394</v>
       </c>
       <c r="K33" t="n">
-        <v>9.0366859944058</v>
+        <v>9.03665996827394</v>
       </c>
       <c r="L33" t="n">
-        <v>0.022281138654952</v>
+        <v>0.0222508679981077</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0340765156051243</v>
+        <v>0.0339178517557966</v>
       </c>
       <c r="N33" t="n">
-        <v>0.284679106703416</v>
+        <v>0.292251623880635</v>
       </c>
     </row>
     <row r="34">
@@ -2062,7 +2062,7 @@
         <v>182</v>
       </c>
       <c r="E34" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="F34" t="n">
         <v>5</v>
@@ -2071,25 +2071,25 @@
         <v>27</v>
       </c>
       <c r="H34" t="n">
-        <v>1387.41759635406</v>
+        <v>1387.41760978249</v>
       </c>
       <c r="I34" t="n">
-        <v>1359.96569721328</v>
+        <v>1359.96573989669</v>
       </c>
       <c r="J34" t="n">
-        <v>-9.58070827783086</v>
+        <v>-9.58069946927714</v>
       </c>
       <c r="K34" t="n">
-        <v>9.58070827783086</v>
+        <v>9.58069946927714</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0125438705754409</v>
+        <v>0.0125700670390765</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0177477532004949</v>
+        <v>0.0177943215267454</v>
       </c>
       <c r="N34" t="n">
-        <v>0.828477775141443</v>
+        <v>0.826922370130755</v>
       </c>
     </row>
     <row r="35">
@@ -2106,7 +2106,7 @@
         <v>183</v>
       </c>
       <c r="E35" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="F35" t="n">
         <v>5</v>
@@ -2115,25 +2115,25 @@
         <v>27</v>
       </c>
       <c r="H35" t="n">
-        <v>1436.65076765472</v>
+        <v>1436.65076852872</v>
       </c>
       <c r="I35" t="n">
-        <v>1411.39730435077</v>
+        <v>1411.3973064907</v>
       </c>
       <c r="J35" t="n">
-        <v>-10.0308385014458</v>
+        <v>-10.0308445173025</v>
       </c>
       <c r="K35" t="n">
-        <v>10.0308385014458</v>
+        <v>10.0308445173025</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0144069781372692</v>
+        <v>0.0140753227389153</v>
       </c>
       <c r="M35" t="n">
-        <v>0.0220853263726107</v>
+        <v>0.0219225994735892</v>
       </c>
       <c r="N35" t="n">
-        <v>0.720429234157519</v>
+        <v>0.726668096789906</v>
       </c>
     </row>
     <row r="36">
@@ -2150,7 +2150,7 @@
         <v>184</v>
       </c>
       <c r="E36" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F36" t="n">
         <v>5</v>
@@ -2159,25 +2159,25 @@
         <v>27</v>
       </c>
       <c r="H36" t="n">
-        <v>1405.11936247541</v>
+        <v>1405.11931873838</v>
       </c>
       <c r="I36" t="n">
-        <v>1377.80922128502</v>
+        <v>1377.80924238662</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.05766919292148</v>
+        <v>-9.05755046911874</v>
       </c>
       <c r="K36" t="n">
-        <v>9.05766919292148</v>
+        <v>9.05755046911874</v>
       </c>
       <c r="L36" t="n">
-        <v>0.0208162109055575</v>
+        <v>0.0211052017980199</v>
       </c>
       <c r="M36" t="n">
-        <v>0.0281419003052426</v>
+        <v>0.028641404446813</v>
       </c>
       <c r="N36" t="n">
-        <v>0.534713189719581</v>
+        <v>0.527500695448696</v>
       </c>
     </row>
   </sheetData>
